--- a/files/ModelRMS_for_mexicanWorkshop.xlsx
+++ b/files/ModelRMS_for_mexicanWorkshop.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulisboa-my.sharepoint.com/personal/ist1100262_tecnico_ulisboa_pt/Documents/MEMec/Thesis/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{4B5E4742-C142-4AC4-B6F3-A64487A8B7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AFC9609-75B1-41C0-9247-0E40E4319CFD}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{4B5E4742-C142-4AC4-B6F3-A64487A8B7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EA4F187-B600-4845-96D0-30422172388F}"/>
   <bookViews>
-    <workbookView xWindow="2376" yWindow="1944" windowWidth="23040" windowHeight="12660" activeTab="1" xr2:uid="{00B3B602-F47A-45B0-8AAE-B7D828EC3A00}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00B3B602-F47A-45B0-8AAE-B7D828EC3A00}"/>
   </bookViews>
   <sheets>
     <sheet name="clean" sheetId="1" r:id="rId1"/>
     <sheet name="noise0.01" sheetId="3" r:id="rId2"/>
+    <sheet name="wn" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5135,4 +5136,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF03C906-1AAE-45CC-9B11-2A5D03610DA7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>